--- a/research/traditional_assets/database/data/oman/oman_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_banks_regional.xlsx
@@ -588,7 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.204</v>
+        <v>0.159</v>
+      </c>
+      <c r="E2">
+        <v>0.368</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>30.2</v>
+        <v>36.8</v>
       </c>
       <c r="L2">
-        <v>0.3254310344827586</v>
+        <v>0.3445692883895131</v>
       </c>
       <c r="M2">
-        <v>4.88</v>
+        <v>20</v>
       </c>
       <c r="N2">
-        <v>0.008657087103069007</v>
+        <v>0.03434065934065934</v>
       </c>
       <c r="O2">
-        <v>0.1615894039735099</v>
+        <v>0.5434782608695653</v>
       </c>
       <c r="P2">
-        <v>4.88</v>
+        <v>20</v>
       </c>
       <c r="Q2">
-        <v>0.008657087103069007</v>
+        <v>0.03434065934065934</v>
       </c>
       <c r="R2">
-        <v>0.1615894039735099</v>
+        <v>0.5434782608695653</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>202.3</v>
+        <v>115.9</v>
       </c>
       <c r="V2">
-        <v>0.3588788362604222</v>
+        <v>0.1990041208791209</v>
       </c>
       <c r="W2">
-        <v>0.07425620850749938</v>
+        <v>0.05967245013783038</v>
       </c>
       <c r="X2">
-        <v>0.1780987338808585</v>
+        <v>0.08264735064301157</v>
       </c>
       <c r="Y2">
-        <v>-0.1038425253733591</v>
+        <v>-0.02297490050518119</v>
       </c>
       <c r="Z2">
-        <v>0.3996554694229113</v>
+        <v>0.05637668918918919</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08234741702309342</v>
+        <v>0.08264735064301157</v>
       </c>
       <c r="AC2">
-        <v>-0.08234741702309342</v>
+        <v>-0.08264735064301157</v>
       </c>
       <c r="AD2">
-        <v>1480</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1480</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>1277.7</v>
+        <v>-115.9</v>
       </c>
       <c r="AH2">
-        <v>0.7241767382688261</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.7058711308246293</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.6938742261322907</v>
+        <v>-0.2484458735262594</v>
       </c>
       <c r="AK2">
-        <v>0.6744615709459459</v>
+        <v>-0.2267657992565056</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,7 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.204</v>
+        <v>0.159</v>
+      </c>
+      <c r="E3">
+        <v>0.368</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>30.2</v>
+        <v>36.8</v>
       </c>
       <c r="L3">
-        <v>0.3254310344827586</v>
+        <v>0.3445692883895131</v>
       </c>
       <c r="M3">
-        <v>4.88</v>
+        <v>20</v>
       </c>
       <c r="N3">
-        <v>0.008657087103069007</v>
+        <v>0.03434065934065934</v>
       </c>
       <c r="O3">
-        <v>0.1615894039735099</v>
+        <v>0.5434782608695653</v>
       </c>
       <c r="P3">
-        <v>4.88</v>
+        <v>20</v>
       </c>
       <c r="Q3">
-        <v>0.008657087103069007</v>
+        <v>0.03434065934065934</v>
       </c>
       <c r="R3">
-        <v>0.1615894039735099</v>
+        <v>0.5434782608695653</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>202.3</v>
+        <v>115.9</v>
       </c>
       <c r="V3">
-        <v>0.3588788362604222</v>
+        <v>0.1990041208791209</v>
       </c>
       <c r="W3">
-        <v>0.07425620850749938</v>
+        <v>0.05967245013783038</v>
       </c>
       <c r="X3">
-        <v>0.1780987338808585</v>
+        <v>0.08264735064301157</v>
       </c>
       <c r="Y3">
-        <v>-0.1038425253733591</v>
+        <v>-0.02297490050518119</v>
       </c>
       <c r="Z3">
-        <v>0.3996554694229113</v>
+        <v>0.05637668918918919</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08234741702309342</v>
+        <v>0.08264735064301157</v>
       </c>
       <c r="AC3">
-        <v>-0.08234741702309342</v>
+        <v>-0.08264735064301157</v>
       </c>
       <c r="AD3">
-        <v>1480</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1480</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1277.7</v>
+        <v>-115.9</v>
       </c>
       <c r="AH3">
-        <v>0.7241767382688261</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.7058711308246293</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.6938742261322907</v>
+        <v>-0.2484458735262594</v>
       </c>
       <c r="AK3">
-        <v>0.6744615709459459</v>
+        <v>-0.2267657992565056</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/oman/oman_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.159</v>
+        <v>0.134</v>
       </c>
       <c r="E2">
-        <v>0.368</v>
+        <v>0.215</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>36.8</v>
+        <v>41.6</v>
       </c>
       <c r="L2">
-        <v>0.3445692883895131</v>
+        <v>0.3639545056867892</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>23.5</v>
       </c>
       <c r="N2">
-        <v>0.03434065934065934</v>
+        <v>0.04212979562567229</v>
       </c>
       <c r="O2">
-        <v>0.5434782608695653</v>
+        <v>0.5649038461538461</v>
       </c>
       <c r="P2">
-        <v>20</v>
+        <v>23.5</v>
       </c>
       <c r="Q2">
-        <v>0.03434065934065934</v>
+        <v>0.04212979562567229</v>
       </c>
       <c r="R2">
-        <v>0.5434782608695653</v>
+        <v>0.5649038461538461</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>115.9</v>
+        <v>254.3</v>
       </c>
       <c r="V2">
-        <v>0.1990041208791209</v>
+        <v>0.4558981713875942</v>
       </c>
       <c r="W2">
-        <v>0.05967245013783038</v>
+        <v>0.06634768740031897</v>
       </c>
       <c r="X2">
-        <v>0.08264735064301157</v>
+        <v>0.06297929771099899</v>
       </c>
       <c r="Y2">
-        <v>-0.02297490050518119</v>
+        <v>0.003368389689319989</v>
       </c>
       <c r="Z2">
-        <v>0.05637668918918919</v>
+        <v>0.2236352964194874</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08264735064301157</v>
+        <v>0.06297929771099899</v>
       </c>
       <c r="AC2">
-        <v>-0.08264735064301157</v>
+        <v>-0.06297929771099899</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-115.9</v>
+        <v>-254.3</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2484458735262594</v>
+        <v>-0.8378912685337728</v>
       </c>
       <c r="AK2">
-        <v>-0.2267657992565056</v>
+        <v>-0.6512163892445584</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.159</v>
+        <v>0.134</v>
       </c>
       <c r="E3">
-        <v>0.368</v>
+        <v>0.215</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>36.8</v>
+        <v>41.6</v>
       </c>
       <c r="L3">
-        <v>0.3445692883895131</v>
+        <v>0.3639545056867892</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>23.5</v>
       </c>
       <c r="N3">
-        <v>0.03434065934065934</v>
+        <v>0.04212979562567229</v>
       </c>
       <c r="O3">
-        <v>0.5434782608695653</v>
+        <v>0.5649038461538461</v>
       </c>
       <c r="P3">
-        <v>20</v>
+        <v>23.5</v>
       </c>
       <c r="Q3">
-        <v>0.03434065934065934</v>
+        <v>0.04212979562567229</v>
       </c>
       <c r="R3">
-        <v>0.5434782608695653</v>
+        <v>0.5649038461538461</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>115.9</v>
+        <v>254.3</v>
       </c>
       <c r="V3">
-        <v>0.1990041208791209</v>
+        <v>0.4558981713875942</v>
       </c>
       <c r="W3">
-        <v>0.05967245013783038</v>
+        <v>0.06634768740031897</v>
       </c>
       <c r="X3">
-        <v>0.08264735064301157</v>
+        <v>0.06297929771099899</v>
       </c>
       <c r="Y3">
-        <v>-0.02297490050518119</v>
+        <v>0.003368389689319989</v>
       </c>
       <c r="Z3">
-        <v>0.05637668918918919</v>
+        <v>0.2236352964194874</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08264735064301157</v>
+        <v>0.06297929771099899</v>
       </c>
       <c r="AC3">
-        <v>-0.08264735064301157</v>
+        <v>-0.06297929771099899</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-115.9</v>
+        <v>-254.3</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2484458735262594</v>
+        <v>-0.8378912685337728</v>
       </c>
       <c r="AK3">
-        <v>-0.2267657992565056</v>
+        <v>-0.6512163892445584</v>
       </c>
       <c r="AL3">
         <v>0</v>
